--- a/data_extactor/batch_10_fa/batch_0019_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0019_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار شبیه‌سازی ANSYS | AVEVA InTouch HMI | Artisan Studio | Autodesk AutoCAD | Autodesk AutoCAD Mechanical | C | C# | C++ | نرم‌افزار مهندسی نرم‌افزار به کمک کامپیوتر CASE | Dassault Systemes CATIA | Dassault Systemes Dymola | Dassault Systemes SolidWorks | دیباگرها | سیستم‌های فایل دیسک | نرم‌افزار توسعه سیستم‌های نهفته | نرم‌افزار روش اجزای محدود FEM | زبان توصیف سخت‌افزار HDL | IBM Rational | نرم‌افزار اتصال Keysight Intuilink | Linux | MSC Software Adams | MSC Software Nastran | Magellan Firmware | MathWorks Simulink | Mentor Graphics VeSys Design | محیط توسعه یکپارچه Microchip MPLAB IDE | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Modelica | National Instruments LabVIEW | Oracle Java | PTC Creo Parametric | نرم‌افزار کنترل‌کننده منطقی برنامه‌پذیر PLC | Python | نرم‌افزار نمونه‌سازی سریع | نرم‌افزار SAP | نرم‌افزار شبیه‌سازی | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | The MathWorks Real-Time Workshop | The MathWorks Stateflow | زبان مدل‌سازی یکپارچه UML | Vector CANalyzer | Vector CANoe | Vector Canape | نرم‌افزار مرورگر وب | Woodward MotoTron Control Solutions MotoHawk | dSPACE</t>
+          <t>نرم‌افزار شبیه‌سازی ANSYS | AVEVA InTouch HMI | Artisan Studio | Autodesk AutoCAD | Autodesk AutoCAD Mechanical | C | C# | C++ | نرم‌افزار مهندسی نرم‌افزار به کمک کامپیوتر CASE | Dassault Systemes CATIA | Dassault Systemes Dymola | Dassault Systemes SolidWorks | دیباگرها | سیستم‌های فایل دیسک | نرم‌افزار توسعه سیستم‌های تعبیه‌شده | نرم‌افزار روش المان محدود FEM | زبان توصیف سخت‌افزار HDL | IBM Rational | نرم‌افزار اتصال Keysight Intuilink | Linux | MSC Software Adams | MSC Software Nastran | Magellan Firmware | MathWorks Simulink | Mentor Graphics VeSys Design | محیط توسعه یکپارچه Microchip MPLAB IDE | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Modelica | National Instruments LabVIEW | Oracle Java | PTC Creo Parametric | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | Python | نرم‌افزار نمونه‌سازی سریع | نرم‌افزار SAP | نرم‌افزار شبیه‌سازی | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | The MathWorks Real-Time Workshop | The MathWorks Stateflow | زبان مدل‌سازی یکپارچه UML | Vector CANalyzer | Vector CANoe | Vector Canape | نرم‌افزار مرورگر وب | Woodward MotoTron Control Solutions MotoHawk | dSPACE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نوشتن | تفکر انتقادی | درک مطلب | گوش دادن فعال | صحبت کردن | ریاضیات | نظارت | علوم | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>نگارش | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | تولید و فرآوری | مکانیک | ریاضیات | فیزیک | کامپیوتر و الکترونیک</t>
+          <t>مهندسی و فناوری | طراحی | تولید و فرآوری | مکانیک | ریاضیات | فیزیک | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | استدلال قیاسی | بیان نوشتاری | حساسیت به مسئله | استدلال استقرایی | بیان شفاهی | نظم‌دهی اطلاعات | دید نزدیک | روانی ایده‌ها | وضوح گفتار | خلاقیت | تشخیص گفتار | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | توجه انتخابی | دید دور | انعطاف‌پذیری بستار | توانایی عددی</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | بیان شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | وضوح گفتار | اصالت | تشخیص گفتار | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | توجه انتخابی | بینایی دور | انعطاف‌پذیری بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تماس با دیگران | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | تکرار تصمیم‌گیری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید | نقشه‌کشان مکانیک | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان میکروسیستم | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان میکروسیستم | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ANSYS LS-DYNA | ANSYS Multiphysics | Adobe Photoshop | شبیه‌سازی اچ کریستالی ناهمسانگرد ACES | Ansys Fluent | Apple macOS | Autodesk AutoCAD | Bash | نرم‌افزار Beige Bag B2 Spice | C | C# | C++ | CAzM | COMSOL Multiphysics | Cadence PSpice | نرم‌افزار شبیه‌سازی مدار | Coventor ARCHITECT3D | Coventor CoventorWare | Dassault Systemes Abaqus | Dassault Systemes SolidWorks | نرم‌افزار دیباگ | Dolphin Integration SMASH | شبیه‌ساز طراحی شیءگرای فلوریدا FLOODS | شبیه‌ساز فرآیند شیءگرای فلوریدا FLOOPS | Facebook | نرم‌افزار تحلیل اجزای محدود FEA | نرم‌افزار روش اجزای محدود FEM | Git | IRSIM | IntelliCAD | Intusoft ICAP | JavaScript | KLA-Tencor PROLITH | Linear Technology LTSpice | Linux | MEMSCAP MEMS Pro | MSC Software Patran | Mentor Graphics LeonardoSpectrum | نرم‌افزار شبیه‌سازی سیستم‌های میکروالکترومکانیکی MEMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visual Basic | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Microwind Dsch | Minitab | نرم‌افزار تجسم مولکولی | National Instruments LabVIEW | Oracle Java | PISCES IIB | PTC Creo Parametric | Penzar TopSPICE | Perl | نرم‌افزار شبیه‌سازی فرآیند | Python | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | نرم‌افزار SAP | SAS | SAS JMP | SUPREM | نرم‌افزار ثبت شماتیک | اسکریپت Shell | Siemens ModelSim | نرم‌افزار Siemens PLM | SimWindows | برنامه شبیه‌سازی با تأکید بر مدار مجتمع SPICE | نرم‌افزار شبیه‌سازی | سیستم طراحی VLSI الکتریکی نرم‌افزار Static Free | نرم‌افزار کنترل فرآیند آماری SPC | Syborg Systems MicroTec | Synopsys HSPICE | Synopsys Taurus Medici | Tanner EDA L-Edit | Tanner EDA T-SPICE | The MathWorks MATLAB | Transas Group PISCES2 | UNIX | زبان مدل‌سازی یکپارچه UML | Verilog | نرم‌افزار شبیه‌سازی زبان توصیف سخت‌افزار VHSIC با سرعت بسیار بالا VHDL | زبان توصیف سخت‌افزار VHSIC با سرعت بسیار بالا VHDL | نرم‌افزار مرورگر وب | WinSpice | Xcircuit</t>
+          <t>ANSYS LS-DYNA | ANSYS Multiphysics | Adobe Photoshop | شبیه‌سازی اچ کریستالی ناهمسانگرد ACES | Ansys Fluent | Apple macOS | Autodesk AutoCAD | Bash | نرم‌افزار Beige Bag B2 Spice | C | C# | C++ | CAzM | COMSOL Multiphysics | Cadence PSpice | نرم‌افزار شبیه‌سازی مدار | Coventor ARCHITECT3D | Coventor CoventorWare | Dassault Systemes Abaqus | Dassault Systemes SolidWorks | نرم‌افزار عیب‌یابی | Dolphin Integration SMASH | شبیه‌ساز طراحی شیءگرای فلوریدا FLOODS | شبیه‌ساز فرآیند شیءگرای فلوریدا FLOOPS | Facebook | نرم‌افزار تحلیل المان محدود FEA | نرم‌افزار روش المان محدود FEM | Git | IRSIM | IntelliCAD | Intusoft ICAP | JavaScript | KLA-Tencor PROLITH | Linear Technology LTSpice | Linux | MEMSCAP MEMS Pro | MSC Software Patran | Mentor Graphics LeonardoSpectrum | نرم‌افزار شبیه‌سازی سیستم‌های میکروالکترومکانیکی MEMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visual Basic | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Microwind Dsch | Minitab | نرم‌افزار تجسم مولکولی | National Instruments LabVIEW | Oracle Java | PISCES IIB | PTC Creo Parametric | Penzar TopSPICE | Perl | نرم‌افزار شبیه‌سازی فرآیند | Python | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | نرم‌افزار SAP | SAS | SAS JMP | SUPREM | نرم‌افزار ثبت شماتیک | Shell script | Siemens ModelSim | نرم‌افزار Siemens PLM | SimWindows | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | نرم‌افزار شبیه‌سازی | سیستم طراحی VLSI الکتریکی نرم‌افزار Static Free | نرم‌افزار کنترل فرآیند آماری SPC | Syborg Systems MicroTec | Synopsys HSPICE | Synopsys Taurus Medici | Tanner EDA L-Edit | Tanner EDA T-SPICE | The MathWorks MATLAB | Transas Group PISCES2 | UNIX | زبان مدل‌سازی یکپارچه UML | Verilog | نرم‌افزار شبیه‌سازی زبان توصیف سخت‌افزار VHSIC با سرعت بسیار بالا VHDL | زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHSIC VHDL | نرم‌افزار مرورگر وب | WinSpice | Xcircuit</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نوشتن | صحبت کردن | علوم | نظارت | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | علوم | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مهندسی و فناوری | ریاضیات | فیزیک | طراحی | زبان انگلیسی | تولید و فرآوری | مکانیک</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | فیزیک | طراحی | زبان انگلیسی | تولید و فرآوری | مکانیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بیان نوشتاری | نظم‌دهی اطلاعات | روانی ایده‌ها | خلاقیت | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | دید نزدیک | توجه انتخابی | تجسم | استدلال ریاضی | وضوح گفتار | انعطاف‌پذیری بستار | سرعت ادراکی | توانایی عددی | تشخیص رنگ بصری | اشتراک زمانی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | تجسم | استدلال ریاضی | وضوح گفتار | انعطاف‌پذیری بستار | سرعت ادراکی | توانایی عددی | تشخیص رنگ بصری | تقسیم توجه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | مکالمات تلفنی | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان تولید | دانشمندان مواد | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان نانوسیستم | تکنولوژیست‌ها و تکنسین‌های مهندسی نانوتکنولوژی | مهندسان فوتونیک | تکنسین‌های فوتونیک | متخصصان دستگاه شناسایی فرکانس رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک | تکنسین‌های پردازش نیمه‌هادی</t>
+          <t>تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان تولید | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مهندسان فوتونیک | تکنسین‌های فوتونیک | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک | تکنسین‌های فرآوری نیمه‌رساناها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Adept Scientific GRAMS | Apollo Photonics APSS | Autodesk AutoCAD | BPM_CAD | C | C# | C++ | نرم‌افزار نقشه‌کشی یا طراحی به کمک کامپیوتر | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار دیباگ | نرم‌افزار ESRI ArcGIS | نرم‌افزار ESRI | Facebook | نرم‌افزار تحلیل اجزای محدود FEA | ترجمه فرمول/مترجم FORTRAN | Go | Linux | نرم‌افزار نقشه‌برداری | Mathsoft Mathcad | Microsoft .NET Framework | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | National Instruments LabVIEW | Optical Research Associates LightTools | Optiwave OptiBPM | Optiwave OptiFDTD | Optiwave OptiSPICE | Oracle Java | نرم‌افزار تشخیص الگو | Perl | Photon Design CrystalWave | Photon Design FIMMPROP | Photon Design FIMMWAVE | Photon Design OmniSim | Photon Design PICWave | Python | QGIS | R | SAS | اسکریپت Shell | نرم‌افزار طیف‌سنجی | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | UNIX | Wolfram Research Mathematica | Zemax</t>
+          <t>Adept Scientific GRAMS | Apollo Photonics APSS | Autodesk AutoCAD | BPM_CAD | C | C# | C++ | نرم‌افزار نقشه‌کشی یا طراحی به کمک کامپیوتر | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار عیب‌یابی | نرم‌افزار ESRI ArcGIS | نرم‌افزار ESRI | Facebook | نرم‌افزار تحلیل المان محدود FEA | Formula translation/translator FORTRAN | Go | Linux | نرم‌افزار نقشه‌برداری | Mathsoft Mathcad | Microsoft .NET Framework | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | National Instruments LabVIEW | Optical Research Associates LightTools | Optiwave OptiBPM | Optiwave OptiFDTD | Optiwave OptiSPICE | Oracle Java | نرم‌افزار تشخیص الگو | Perl | Photon Design CrystalWave | Photon Design FIMMPROP | Photon Design FIMMWAVE | Photon Design OmniSim | Photon Design PICWave | Python | QGIS | R | SAS | Shell script | نرم‌افزار طیف‌سنجی | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | UNIX | Wolfram Research Mathematica | Zemax</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نوشتن | گوش دادن فعال | ریاضیات | صحبت کردن | یادگیری فعال | علوم | استراتژی‌های یادگیری | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | گوش دادن فعال | ریاضیات | سخن گفتن | یادگیری فعال | علوم | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | فیزیک | ریاضیات | کامپیوتر و الکترونیک | طراحی | زبان انگلیسی | مکانیک</t>
+          <t>مهندسی و فناوری | فیزیک | ریاضیات | رایانه و الکترونیک | طراحی | زبان انگلیسی | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | درک نوشتاری | درک شنیداری | استدلال ریاضی | بیان نوشتاری | روانی ایده‌ها | خلاقیت | حساسیت به مسئله | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | دید نزدیک | وضوح گفتار | توانایی عددی | انعطاف‌پذیری بستار | تشخیص گفتار | تجسم | سرعت ادراکی</t>
+          <t>استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک کتبی | درک شفاهی | استدلال ریاضی | بیان کتبی | روانی ایده‌ها | اصالت | حساسیت به مسئله | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | وضوح گفتار | توانایی عددی | انعطاف‌پذیری بستار | تشخیص گفتار | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | تماس با دیگران | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | سطح رقابت</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | ارتباط با دیگران | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | سطح رقابت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | دانشمندان مواد | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان نانوسیستم | تکنولوژیست‌ها و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک | متخصصان دستگاه شناسایی فرکانس رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AVEVA InTouch HMI | نرم‌افزار Amazon Web Services AWS | Atlassian JIRA | Autodesk AutoCAD | Bentley MicroStation | C | C# | C++ | CODESYS | کامپایلرها | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | ابزارهای مهندسی نرم‌افزار به کمک کامپیوتر CASE | نرم‌افزار مهندسی به کمک کامپیوتر CAE | سیستم‌های نسخه‌بندی همزمان | Dassault Systemes CATIA | Dassault Systemes SolidWorks | دیباگرها | نرم‌افزار تحلیل اجزای محدود FEA | GRASPIT! | Gazebo | Git | نرم‌افزار سازنده رابط کاربری گرافیکی GUI | Haskell | نرم‌افزار رابط انسان و ماشین HMI | پردازشگرهای تصویر | JavaScript | Keb Combivis Studio | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | منطق نردبانی | Linux | زبان پردازش لیست LISP | MathWorks Simulink | Microsoft .NET Framework | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | National Instruments LabVIEW | Oracle Database | Oracle Java | Presagis Stage | پروفایلرها | نرم‌افزار کنترل‌کننده منطقی برنامه‌پذیر PLC | Python | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | آکادمی رباتیک ROBOTC | Rockwell RSLogix | Siemens SIMATIC STEP 7 | Siemens SIMATIC WinCC | ابزارهای توسعه نرم‌افزار | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | نرم‌افزار تست | The MathWorks MATLAB | UNIX | USyCaMs | نرم‌افزار درایو فرکانس متغیر VFD | نرم‌افزار کنترل نسخه | دیجیتایزرهای ویدئویی | Wind River Systems VxWorks | Windows Embedded Compact</t>
+          <t>AVEVA InTouch HMI | نرم‌افزار Amazon Web Services AWS | Atlassian JIRA | Autodesk AutoCAD | Bentley MicroStation | C | C# | C++ | CODESYS | کامپایلرها | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | ابزارهای مهندسی نرم‌افزار به کمک کامپیوتر CASE | نرم‌افزار مهندسی به کمک کامپیوتر CAE | سیستم‌های نسخه‌بندی همزمان | Dassault Systemes CATIA | Dassault Systemes SolidWorks | دیباگرها | نرم‌افزار تحلیل المان محدود FEA | GRASPIT! | Gazebo | Git | نرم‌افزار سازنده رابط کاربری گرافیکی GUI | Haskell | نرم‌افزار رابط انسان و ماشین HMI | پردازشگرهای تصویر | JavaScript | Keb Combivis Studio | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Ladder Logic | Linux | زبان پردازش لیست LISP | MathWorks Simulink | Microsoft .NET Framework | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | National Instruments LabVIEW | Oracle Database | Oracle Java | Presagis Stage | پروفایلرها | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | Python | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | آکادمی رباتیک ROBOTC | Rockwell RSLogix | Siemens SIMATIC STEP 7 | Siemens SIMATIC WinCC | ابزارهای توسعه نرم‌افزار | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار آزمون | The MathWorks MATLAB | UNIX | USyCaMs | نرم‌افزار درایو فرکانس متغیر VFD | نرم‌افزار کنترل نسخه | دیجیتایزرهای ویدئویی | Wind River Systems VxWorks | Windows Embedded Compact</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | نوشتن | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری | صحبت کردن | علوم</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | سخن گفتن | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | کامپیوتر و الکترونیک | مکانیک | ریاضیات | زبان انگلیسی | فیزیک | تولید و فرآوری | آموزش و پرورش</t>
+          <t>مهندسی و فناوری | طراحی | رایانه و الکترونیک | مکانیک | ریاضیات | زبان انگلیسی | فیزیک | تولید و فرآوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شنیداری | درک نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | روانی ایده‌ها | خلاقیت | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | تجسم | بیان شفاهی | بیان نوشتاری | دید نزدیک | انعطاف‌پذیری بستار | تشخیص گفتار | مهارت انگشتان | توانایی عددی | سرعت ادراکی | وضوح گفتار | تشخیص رنگ بصری | ثبات دست و بازو | توجه انتخابی | دقت کنترل | مهارت دستی | اشتراک زمانی | حافظه</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | تجسم | بیان شفاهی | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری بستار | تشخیص گفتار | مهارت انگشتان | توانایی عددی | سرعت ادراکی | وضوح گفتار | تشخیص رنگ بصری | ثبات دست و بازو | توجه انتخابی | دقت کنترل | مهارت دستی | تقسیم توجه | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تماس با دیگران | فشار زمانی | سلامت و ایمنی سایر کارگران | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تکرار تصمیم‌گیری | پیامد خطا | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | فشار زمانی | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | مهندسان هوافضا | مهندسان خودرو | مهندسان سخت‌افزار کامپیوتر | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان تولید | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | تکنولوژیست‌ها و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | مهندسان خودرو | مهندسان سخت‌افزار کامپیوتر | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AWS Elastic MapReduce (EMR) | Adobe FreeHand MX | Apache Hadoop | Apache MXNet | Autodesk AutoCAD | Breault Research ASAP | CP2K | CPMD | CSC Elmer | DL_POLY | Dassault Systemes Abaqus | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | ESA MOSAICS | نرم‌افزار تفاضل محدود در حوزه زمان FDTD | GE Healthcare Centricity EMR | سیستم ساختار الکترونیکی اتمی و مولکولی عمومی اتمی GAMESS | IMSI Design DesignCAD | شبیه‌ساز دینامیک مولکولی LAMMPS | LinkCAD | Linux | MAYA Nastran | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Windows | Microsoft Word | NWChem | National Instruments LabVIEW | Optical Research Associates LightTools | Oracle Database | Oracle Java | Oracle Manufacturing Scheduling | PTC Creo Parametric | Python | QuantumWise Atomistix ToolKit | نرم‌افزار نمونه‌سازی سریع | نرم‌افزار SAP | SEMC-2D | نرم‌افزار Salesforce | نرم‌افزار شبیه‌سازی | زبان پرس‌وجوی ساختاریافته SQL | Tableau | Tanner EDA L-Edit | UTQUANT | بسته شبیه‌سازی اب-اینیتو وین VASP</t>
+          <t>AWS Elastic MapReduce (EMR) | Adobe FreeHand MX | Apache Hadoop | Apache MXNet | Autodesk AutoCAD | Breault Research ASAP | CP2K | CPMD | CSC Elmer | DL_POLY | Dassault Systemes Abaqus | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | ESA MOSAICS | نرم‌افزار حوزه زمان تفاضل محدود FDTD | GE Healthcare Centricity EMR | سیستم ساختار الکترونیکی اتمی و مولکولی عمومی اتمی GAMESS | IMSI Design DesignCAD | شبیه‌ساز دینامیک مولکولی LAMMPS | LinkCAD | Linux | MAYA Nastran | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Windows | Microsoft Word | NWChem | National Instruments LabVIEW | Optical Research Associates LightTools | Oracle Database | Oracle Java | Oracle Manufacturing Scheduling | PTC Creo Parametric | Python | QuantumWise Atomistix ToolKit | نرم‌افزار نمونه‌سازی سریع | نرم‌افزار SAP | SEMC-2D | نرم‌افزار Salesforce | نرم‌افزار شبیه‌سازی | زبان پرس‌وجوی ساختاریافته SQL | Tableau | Tanner EDA L-Edit | UTQUANT | بسته شبیه‌سازی اب-اینیتو وین VASP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>صحبت کردن | درک مطلب | تفکر انتقادی | علوم | گوش دادن فعال | نوشتن | ریاضیات | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | علوم | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | فیزیک | شیمی | ریاضیات | کامپیوتر و الکترونیک | زبان انگلیسی | آموزش و پرورش | طراحی | تولید و فرآوری | مکانیک | مدیریت و اداره</t>
+          <t>مهندسی و فناوری | فیزیک | شیمی | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | طراحی | تولید و فرآوری | مکانیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | استدلال ریاضی | انعطاف‌پذیری بستار | خلاقیت | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | توانایی عددی | توجه انتخابی | تجسم | دید دور</t>
+          <t>استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | استدلال ریاضی | انعطاف‌پذیری بستار | اصالت | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | توانایی عددی | توجه انتخابی | تجسم | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | مکالمات تلفنی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارگران | تماس با دیگران | سطح رقابت</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | سطح رقابت</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دان‌ها و بیوفیزیک‌دان‌ها | مهندسان زیستی و مهندسان پزشکی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | دانشمندان بیوانفورماتیک | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دان‌ها | مهندسان پیل سوختی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان تولید | مهندسان مواد | دانشمندان مواد | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | زیست‌شناسان مولکولی و سلولی | تکنولوژیست‌ها و تکنسین‌های مهندسی نانوتکنولوژی | مهندسان فوتونیک | تکنسین‌های فوتونیک | مهندسان رباتیک</t>
+          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | دانشمندان بیوانفورماتیک | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | مهندسان پیل سوختی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان تولید | مهندسان مواد | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | زیست‌شناسان مولکولی و سلولی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مهندسان فوتونیک | تکنسین‌های فوتونیک | مهندسان رباتیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار شبیه‌سازی ANSYS | نرم‌افزار Amazon Web Services AWS | Apache Ant | Apache Subversion SVN | Autodesk AutoCAD | Bentley MicroStation | C# | C++ | نرم‌افزار دینامیک سیالات محاسباتی CFD | DIgSILENT PowerFactory | Dassault Systemes SolidWorks | EMD International WindPRO | ESRI ArcGIS Spatial Analyst | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | زبان نشانه‌گذاری توسعه‌پذیر XML | ترجمه فرمول/مترجم FORTRAN | نرم‌افزار جریان بار توالی مثبت GE Energy PSLF | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | نرم‌افزار Global Mapper | Google Earth Pro | JUnit | Linux | Manitoba HVDC Research Centre PSCAD | Mathsoft Mathcad | Microsoft .NET Framework | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Basic | نسخه اسکریپت‌نویسی Microsoft Visual Basic VBScript | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual Studio | Microsoft Word | National Instruments LabVIEW | Oracle Java | Oracle Primavera Systems | PTC Creo Parametric | نرم‌افزار مدل‌سازی سیستم قدرت | PowerWorld Corporation PowerWorld Simulator | Python | ReSoft WindFarm | برنامه تحلیل و کاربرد اطلس باد آزمایشگاه ملی Risoe WAsP | ابزارهای قدرت تحلیل سیستم‌های SKM | Schneider Electric Direct Coordination | مجموعه محصول Siemens PSS | ابزارهای توسعه نرم‌افزار | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | Tableau | The MathWorks MATLAB | UNIX | نرم‌افزار مرورگر وب | نرم‌افزار کنفرانس وب | WindSim | نرم‌افزار Wonderware</t>
+          <t>نرم‌افزار شبیه‌سازی ANSYS | نرم‌افزار Amazon Web Services AWS | Apache Ant | Apache Subversion SVN | Autodesk AutoCAD | Bentley MicroStation | C# | C++ | نرم‌افزار دینامیک سیالات محاسباتی CFD | DIgSILENT PowerFactory | Dassault Systemes SolidWorks | EMD International WindPRO | ESRI ArcGIS Spatial Analyst | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | زبان نشانه‌گذاری توسعه‌پذیر XML | Formula translation/translator FORTRAN | نرم‌افزار جریان بار توالی مثبت GE Energy PSLF | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | Global Mapper Software Global Mapper | Google Earth Pro | JUnit | Linux | Manitoba HVDC Research Centre PSCAD | Mathsoft Mathcad | Microsoft .NET Framework | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual Studio | Microsoft Word | National Instruments LabVIEW | Oracle Java | Oracle Primavera Systems | PTC Creo Parametric | نرم‌افزار مدل‌سازی سیستم قدرت | PowerWorld Corporation PowerWorld Simulator | Python | ReSoft WindFarm | برنامه تحلیل و کاربرد اطلس باد آزمایشگاه ملی Risoe WAsP | ابزارهای قدرت تحلیل سیستم‌های SKM | Schneider Electric Direct Coordination | مجموعه محصول Siemens PSS | ابزارهای توسعه نرم‌افزار | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Tableau | The MathWorks MATLAB | UNIX | نرم‌افزار مرورگر وب | نرم‌افزار کنفرانس وب | WindSim | نرم‌افزار Wonderware</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | ریاضیات | گوش دادن فعال | نوشتن | صحبت کردن | علوم | نظارت | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | ریاضیات | گوش دادن فعال | نگارش | سخن گفتن | علوم | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | طراحی | فیزیک | زبان انگلیسی | کامپیوتر و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مکانیک | ایمنی و امنیت عمومی | قانون و دولت</t>
+          <t>مهندسی و فناوری | ریاضیات | طراحی | فیزیک | زبان انگلیسی | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مکانیک | ایمنی و امنیت عمومی | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | درک نوشتاری | توانایی عددی | حساسیت به مسئله | درک شنیداری | بیان نوشتاری | بیان شفاهی | وضوح گفتار | دید نزدیک | تشخیص گفتار | تجسم | نظم‌دهی اطلاعات | خلاقیت | روانی ایده‌ها</t>
+          <t>استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | درک کتبی | توانایی عددی | حساسیت به مسئله | درک شفاهی | بیان کتبی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | تجسم | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | فشار زمانی | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | فشار زمانی | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان هوافضا | مهندسان خودرو | مدیران نیروگاه زیست‌توده | مهندسان عمران | مهندسان برق | مهندسان انرژی، به جز باد و خورشید | مدیران تولید زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | توزیع‌کنندگان و دیسپاچرهای برق | اپراتورهای نیروگاه | مهندسان سیستم‌های انرژی خورشیدی | نصاب‌های فتوولتائیک خورشیدی | مهندسان آب/فاضلاب | مدیران توسعه انرژی بادی | مدیران عملیات انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
+          <t>مهندسان هوافضا | مهندسان خودرو | مدیران نیروگاه‌های زیست‌توده | مهندسان عمران | مهندسان برق | مهندسان انرژی، به جز باد و خورشید | مدیران تولید زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی | مدیران عملیات انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ansys Fluent | Aurora HelioScope | Autodesk AutoCAD | Autodesk AutoCAD LT | Autodesk Revit | Bash | C++ | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | نرم‌افزار تجسم داده | نرم‌افزار پایگاه داده | نرم‌افزار دیباگ | ETAP | Energy-10 | نرم‌افزار روش اجزای محدود FEM | سیستم‌های اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | نرم‌افزار Google Workspace | مدل بهینه‌سازی میکروتوان HOMER | IMSI TurboCAD | JavaScript | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | سیستم National Instruments Compact FieldPoint | National Instruments LabVIEW | Optical Physics Technologies SUN_CHART | Oracle Hyperion | PV Optics | PVsyst | Python | ابزارهای Python برای Visual Studio (PTVS) | R | RETScreen | سیستم استقرار انرژی منطقه‌ای ReEDS | ابزارهای قدرت تحلیل سیستم‌های SKM | SOLAR-2 | نرم‌افزار Salesforce | مدل ساده انتقال تابشی جوی خورشید SMARTS | نرم‌افزار شبیه‌سازی | ابزارهای توسعه نرم‌افزار | SolTrace | مدل مشاور خورشیدی | ارزیابی منابع انرژی خورشیدی و بادی SWERA | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | The MathWorks MATLAB | Trimble SketchUp Pro</t>
+          <t>Ansys Fluent | Aurora HelioScope | Autodesk AutoCAD | Autodesk AutoCAD LT | Autodesk Revit | Bash | C++ | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | نرم‌افزار تجسم داده | نرم‌افزار پایگاه داده | نرم‌افزار عیب‌یابی | ETAP | Energy-10 | نرم‌افزار روش المان محدود FEM | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | نرم‌افزار Google Workspace | مدل بهینه‌سازی میکروتوان HOMER | IMSI TurboCAD | JavaScript | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | سیستم National Instruments Compact FieldPoint | National Instruments LabVIEW | Optical Physics Technologies SUN_CHART | Oracle Hyperion | PV Optics | PVsyst | Python | ابزارهای Python برای Visual Studio (PTVS) | R | RETScreen | سیستم استقرار انرژی منطقه‌ای ReEDS | ابزارهای قدرت تحلیل سیستم‌های SKM | SOLAR-2 | نرم‌افزار Salesforce | مدل ساده انتقال تابشی جوی خورشید SMARTS | نرم‌افزار شبیه‌سازی | ابزارهای توسعه نرم‌افزار | SolTrace | مدل مشاور خورشیدی | ارزیابی منابع انرژی خورشیدی و بادی SWERA | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | The MathWorks MATLAB | Trimble SketchUp Pro</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نوشتن | صحبت کردن | گوش دادن فعال | ریاضیات | نظارت | یادگیری فعال | علوم</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | ریاضیات | نظارت | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | ساختمان و ساخت‌وساز | ریاضیات | مکانیک | فیزیک | کامپیوتر و الکترونیک | مدیریت و اداره | زبان انگلیسی</t>
+          <t>مهندسی و فناوری | طراحی | ساختمان و ساخت‌وساز | ریاضیات | مکانیک | فیزیک | رایانه و الکترونیک | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | درک نوشتاری | بیان شفاهی | روانی ایده‌ها | استدلال استقرایی | درک شنیداری | نظم‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | خلاقیت | دید نزدیک | وضوح گفتار | تشخیص گفتار | تجسم | انعطاف‌پذیری بستار | توانایی عددی | دید دور | توجه انتخابی</t>
+          <t>بیان کتبی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بیان شفاهی | روانی ایده‌ها | استدلال استقرایی | درک شفاهی | ترتیب‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | اصالت | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | تجسم | انعطاف‌پذیری بستار | توانایی عددی | بینایی دور | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | فشار زمانی | اهمیت دقیق یا صحیح بودن | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارگران | نتایج کاری و خروجی‌های سایر کارگران | محیط خارجی، در معرض تمام شرایط آب و هوایی | پیامد خطا | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | محیط داخلی، بدون کنترل محیطی | برخورد با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>مکالمات تلفنی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | فشار زمانی | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، بدون کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | ممیزان انرژی | مهندسان انرژی، به جز باد و خورشید | مهندسان پیل سوختی | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مهندسان مکانیک | مدیران نصب انرژی خورشیدی | نصاب‌های فتوولتائیک خورشیدی | نمایندگان فروش و ارزیابان خورشیدی | نصاب‌ها و تکنسین‌های حرارتی خورشیدی | مهندسان آب/فاضلاب | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
+          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | بازرسان انرژی | مهندسان انرژی، به جز باد و خورشید | مهندسان پیل سوختی | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مهندسان مکانیک | مدیران نصب انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | نمایندگان و ارزیابان فروش تجهیزات خورشیدی | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>کتابخانه الگوی هاش 100 پلاس | ARCOM Masterspec | Adobe Acrobat | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe LiveMotion | Adobe Photoshop | Alias Wavefront Design Studio | نرم‌افزار انیمیشن | AutoDesSys form Z | Autodesk 3d Studio Viz | Autodesk 3ds Max | Autodesk Architectural Desktop | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Inventor | Autodesk Land Desktop | Autodesk Navisworks | Autodesk Revit | Autodesk Revit Architecture | Autodesk Softdesk | Bentley GeoPak Bridge | Bentley MicroStation | Bentley Systems InRoads Suite | Bentley WaterCAD | نرم‌افزار صورت‌حساب مواد | نرم‌افزار نقشه‌برداری مرزی | C | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار طراحی به کمک کامپیوتر | Corel Paint Shop Pro | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار پایگاه داده | نرم‌افزار دیجیتالی‌سازی و فتوگرامتری | نرم‌افزار سیستم مدیریت اسناد | ENERCALC FastFrame | نرم‌افزار ERP | نرم‌افزار ESRI ArcGIS | ESRI ArcView | زبان نشانه‌گذاری توسعه‌پذیر XML | سیستم‌های اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی مکانیکی GDA | نرم‌افزار ارائه گرافیکی | Graphisoft ArchiCAD | Intergraph Image Analyst | نرم‌افزار مدل‌سازی منظره | Logitech 3D Pro | McNeel Rhinoceros 3D | Microsoft .NET Framework | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Paint | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Windows | Microsoft Word | نرم‌افزار گرافیک متحرک | NavisWorks Jetstream | نرم‌افزار منحنی‌های B-اسپلاین منطقی غیریکنواخت NURBS | OpenRoads Designer | PTC Creo Parametric | نرم‌افزار طراحی ابزار دقیق و لوله‌کشی PID | نرم‌افزار SAP | نرم‌افزار اسکن | Softimage Extreme | نرم‌افزار مشخصات | SpecsInTact | Sun Microsystems Cobalt | نرم‌افزار Tekla | نرم‌افزار مدل‌سازی سه‌بعدی | نرم‌افزار نقشه توپوگرافی | Trimble SketchUp Pro | UGS Solid Edge | VectorWorks ARCHITECT</t>
+          <t>کتابخانه الگوی هاش 100 پلاس | ARCOM Masterspec | Adobe Acrobat | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe LiveMotion | Adobe Photoshop | Alias Wavefront Design Studio | نرم‌افزار انیمیشن | AutoDesSys form Z | Autodesk 3d Studio Viz | Autodesk 3ds Max | Autodesk Architectural Desktop | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Inventor | Autodesk Land Desktop | Autodesk Navisworks | Autodesk Revit | Autodesk Revit Architecture | Autodesk Softdesk | Bentley GeoPak Bridge | Bentley MicroStation | Bentley Systems InRoads Suite | Bentley WaterCAD | نرم‌افزار صورت‌حساب مواد | نرم‌افزار نقشه‌برداری مرزی | C | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار طراحی به کمک کامپیوتر | Corel Paint Shop Pro | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار پایگاه داده | نرم‌افزار دیجیتالی‌سازی و فتوگرامتری | نرم‌افزار سیستم مدیریت اسناد | ENERCALC FastFrame | نرم‌افزار ERP | نرم‌افزار ESRI ArcGIS | ESRI ArcView | زبان نشانه‌گذاری توسعه‌پذیر XML | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار ارائه گرافیکی | Graphisoft ArchiCAD | Intergraph Image Analyst | نرم‌افزار مدل‌سازی منظره | Logitech 3D Pro | McNeel Rhinoceros 3D | Microsoft .NET Framework | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Paint | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Windows | Microsoft Word | نرم‌افزار گرافیک متحرک | NavisWorks Jetstream | نرم‌افزار منحنی‌های B-اسپلاین منطقی غیریکنواخت NURBS | OpenRoads Designer | PTC Creo Parametric | نرم‌افزار طراحی ابزار دقیق و لوله‌کشی PID | نرم‌افزار SAP | نرم‌افزار اسکن | Softimage Extreme | نرم‌افزار مشخصات | SpecsInTact | Sun Microsystems Cobalt | نرم‌افزار Tekla | نرم‌افزار مدل‌سازی سه‌بعدی | نرم‌افزار نقشه توپوگرافی | Trimble SketchUp Pro | UGS Solid Edge | VectorWorks ARCHITECT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | نوشتن | تفکر انتقادی | یادگیری فعال | ریاضیات | گوش دادن فعال | نظارت | صحبت کردن | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | ریاضیات | گوش دادن فعال | نظارت | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>طراحی | ساختمان و ساخت‌وساز | مهندسی و فناوری | زبان انگلیسی | کامپیوتر و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | مدیریت و اداره</t>
+          <t>طراحی | ساختمان و ساخت‌وساز | مهندسی و فناوری | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تجسم | دید نزدیک | درک شنیداری | درک نوشتاری | بیان نوشتاری | استدلال قیاسی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | استدلال استقرایی | خلاقیت | روانی ایده‌ها | بیان شفاهی | انعطاف‌پذیری بستار | حساسیت به مسئله | توجه انتخابی | وضوح گفتار | تشخیص گفتار | توانایی عددی</t>
+          <t>تجسم | بینایی نزدیک | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | اصالت | روانی ایده‌ها | بیان شفاهی | انعطاف‌پذیری بستار | حساسیت به مسئله | توجه انتخابی | وضوح گفتار | تشخیص گفتار | توانایی عددی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | فشار زمانی | تماس با دیگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف مشابه | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | فشار زمانی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>معماران، به جز منظره و دریایی | مدیران معماری و مهندسی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | طراحان تجاری و صنعتی | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مدیران ساخت‌وساز | بازرسان ساخت‌وساز و ساختمان | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان صنایع | کارگران چیدمان، فلز و پلاستیک | نقشه‌کشان مکانیک | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | توسعه‌دهندگان نرم‌افزار | تکنسین‌های نقشه‌برداری و نقشه‌کشی</t>
+          <t>معماران، به‌جز منظر و دریایی | مدیران معماری و مهندسی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | طراحان تجاری و صنعتی | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان صنایع | کارگران شابلون‌زنی، فلز و پلاستیک | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | توسعه‌دهندگان نرم‌افزار | تکنسین‌های نقشه‌برداری و نقشه‌کشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1CadCam Unigraphics | Adobe Illustrator | Autodesk AutoCAD | Autodesk Navisworks | Autodesk Revit | سیستم مدیریت طراحی کارخانه گروه Aveva PDMS | Bentley AutoPLANT | Bentley I/RAS B | Bentley MicroStation | Bentley PlantSpace SupportModeler | Bentley Systems ProjectWise | Bowen &amp; Groves M1 ERP | C | C++ | COADE CADWorx P&amp;ID | نرم‌افزار Cadence OrCAD | Cadence PSpice | مجموعه چیدمان Cadence Virtuoso | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | مجموعه گرافیکی Corel CorelDraw | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار پایگاه داده مشخصات طراحی | ECT International Raceway Multi-Pack | Epicor Vantage ERP | Exact Software Macola ERP | نرم‌افزار طراحی آرایه دروازه قابل برنامه‌ریزی میدانی FPGA | سیستم‌های اطلاعات جغرافیایی GIS | IBM Lotus Notes | Intergraph INtools | Linux | سرور مجازی Linux | Made2Manage Systems M2M ERP | Magellan Firmware | نرم‌افزار برنامه‌ریزی منابع تولید MRP | MathWorks Simulink | Mentor Graphics Expedition Enterprise | Mentor Graphics PADS | Mentor Graphics Xpedition xDX Designer | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Word | NavisWorks Jetstream | مدیریت پروژه Oracle JD Edwards EnterpriseOne | PCI Express PCIe | PEDYN P2000 | PTC Creo Parametric | PTC Pro/Cable | PTC Pro/INTRALINK | PTC Pro/Pipe | PTC Windchill | Perl | نرم‌افزار کنترل‌کننده منطقی برنامه‌پذیر PLC | Python | نرم‌افزار SAP | ابزارهای قدرت تحلیل سیستم‌های SKM | Sage ERP Accpac | برنامه شبیه‌سازی با تأکید بر مدار مجتمع SPICE | SofTech CADRA | SoftBrands Fourth Shift Edition | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | SystemVerilog | The MathWorks MATLAB | زبان دستور ابزار Tcl | UGS Solid Edge | UNIX | Verilog | نرم‌افزار شبیه‌سازی زبان توصیف سخت‌افزار VHSIC با سرعت بسیار بالا VHDL | Zuken CADSTAR</t>
+          <t>1CadCam Unigraphics | Adobe Illustrator | Autodesk AutoCAD | Autodesk Navisworks | Autodesk Revit | سیستم مدیریت طراحی کارخانه گروه Aveva PDMS | Bentley AutoPLANT | Bentley I/RAS B | Bentley MicroStation | Bentley PlantSpace SupportModeler | Bentley Systems ProjectWise | Bowen &amp; Groves M1 ERP | C | C++ | COADE CADWorx P&amp;ID | نرم‌افزار Cadence OrCAD | Cadence PSpice | Cadence Virtuoso Layout Suite | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Corel CorelDraw Graphics Suite | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار پایگاه داده مشخصات طراحی | ECT International Raceway Multi-Pack | Epicor Vantage ERP | Exact Software Macola ERP | نرم‌افزار طراحی آرایه درگاه قابل برنامه‌ریزی فیلد FPGA | سیستم‌های سیستم اطلاعات جغرافیایی GIS | IBM Lotus Notes | Intergraph INtools | Linux | سرور مجازی Linux | Made2Manage Systems M2M ERP | Magellan Firmware | نرم‌افزار برنامه‌ریزی منابع تولید MRP | MathWorks Simulink | Mentor Graphics Expedition Enterprise | Mentor Graphics PADS | Mentor Graphics Xpedition xDX Designer | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Word | NavisWorks Jetstream | مدیریت پروژه Oracle JD Edwards EnterpriseOne | PCI Express PCIe | PEDYN P2000 | PTC Creo Parametric | PTC Pro/Cable | PTC Pro/INTRALINK | PTC Pro/Pipe | PTC Windchill | Perl | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | Python | نرم‌افزار SAP | ابزارهای قدرت تحلیل سیستم‌های SKM | Sage ERP Accpac | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | SofTech CADRA | SoftBrands Fourth Shift Edition | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | SystemVerilog | The MathWorks MATLAB | زبان دستور ابزار Tcl | UGS Solid Edge | UNIX | Verilog | نرم‌افزار شبیه‌سازی زبان توصیف سخت‌افزار VHSIC با سرعت بسیار بالا VHDL | Zuken CADSTAR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نوشتن | تفکر انتقادی | درک مطلب | یادگیری فعال | صحبت کردن | نظارت</t>
+          <t>گوش دادن فعال | نگارش | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | کامپیوتر و الکترونیک | زبان انگلیسی | ریاضیات | اداری | آموزش و پرورش | ایمنی و امنیت عمومی | جغرافیا</t>
+          <t>طراحی | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | اداری | آموزش و پرورش | ایمنی و امنیت عمومی | جغرافیا</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شنیداری | دید نزدیک | تجسم | بیان شفاهی | بیان نوشتاری | تشخیص گفتار | نظم‌دهی اطلاعات | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
+          <t>درک کتبی | درک شفاهی | بینایی نزدیک | تجسم | بیان شفاهی | بیان کتبی | تشخیص گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | مکالمات تلفنی | فشار زمانی | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | مکالمات تلفنی | فشار زمانی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | طراحان تجاری و صنعتی | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکنندگان تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | مهندسان صنایع | کارگران چیدمان، فلز و پلاستیک | نقشه‌کشان مکانیک | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های رباتیک</t>
+          <t>نقشه‌کشان معماری و عمران | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی عمران | طراحان تجاری و صنعتی | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | مهندسان صنایع | کارگران شابلون‌زنی، فلز و پلاستیک | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | یادگیری فعال | ریاضیات | گوش دادن فعال | درک مطلب | صحبت کردن | نوشتن | نظارت</t>
+          <t>تفکر انتقادی | یادگیری فعال | ریاضیات | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | مکانیک | ریاضیات | زبان انگلیسی | فیزیک | کامپیوتر و الکترونیک | تولید و فرآوری | آموزش و پرورش | خدمات مشتری و شخصی</t>
+          <t>طراحی | مهندسی و فناوری | مکانیک | ریاضیات | زبان انگلیسی | فیزیک | رایانه و الکترونیک | تولید و فرآوری | آموزش و پرورش | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | تجسم | استدلال ریاضی | توجه انتخابی | تشخیص گفتار | وضوح گفتار | درک شنیداری | بیان شفاهی | بیان نوشتاری | روانی ایده‌ها | خلاقیت | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | درک نوشتاری | تشخیص رنگ بصری | مهارت انگشتان | انعطاف‌پذیری بستار | توانایی عددی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات</t>
+          <t>بینایی نزدیک | تجسم | استدلال ریاضی | توجه انتخابی | تشخیص گفتار | وضوح گفتار | درک شفاهی | بیان شفاهی | بیان کتبی | روانی ایده‌ها | اصالت | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | درک کتبی | تشخیص رنگ بصری | مهارت انگشتان | انعطاف‌پذیری بستار | توانایی عددی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | ایمیل | اهمیت دقیق یا صحیح بودن | بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تماس با دیگران | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف مشابه</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | طراحان تجاری و صنعتی | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | کارگران چیدمان، فلز و پلاستیک | ماشین‌کاران | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | سازندگان مدل، فلز و پلاستیک | الگو‌سازان، فلز و پلاستیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>نقشه‌کشان معماری و عمران | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی عمران | طراحان تجاری و صنعتی | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مدل‌سازان فلز و پلاستیک | الگوسازان فلز و پلاستیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0019_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0019_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نگارش | تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | ریاضیات | نظارت | علوم پایه | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>نگارش | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | بیان شفاهی | مرتب‌سازی اطلاعات | دید نزدیک | سیالی ایده | وضوح گفتار | ابتکار | تشخیص گفتار | تجسم فضایی | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | توجه انتخابی | دید دور | انعطاف‌پذیری در نتیجه‌گیری | محاسبات عددی</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | بیان شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | وضوح گفتار | اصالت | تشخیص گفتار | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | توجه انتخابی | بینایی دور | انعطاف‌پذیری بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان ارشد فناوری هوافضا و عملیات پرواز | مهندسان خودرو | تکنسین‌ها و کارشناسان ارشد کالیبراسیون | مهندسان سخت‌افزار رایانه | مهندسان برق | تکنسین‌ها و کارشناسان ارشد مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کارشناسان ارشد الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌استثنای رایانه | تکنسین‌ها و کارشناسان ارشد مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان ارشد مهندسی مکانیک | مهندسان مکانیک | مهندسان میکروسیستم‌ها | تکنسین‌های فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان سخت‌افزار رایانه | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | نقشه‌کشان مکانیک | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | تکنسین‌های فوتونیک و اپتیک | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | علوم | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | مرتب‌سازی اطلاعات | سیالی ایده | ابتکار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | توجه انتخابی | تجسم فضایی | استدلال ریاضی | وضوح گفتار | انعطاف‌پذیری در نتیجه‌گیری | سرعت ادراک | محاسبات عددی | تمایز رنگ‌ها | تقسیم توجه</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | تجسم | استدلال ریاضی | وضوح گفتار | انعطاف‌پذیری بستار | سرعت ادراکی | توانایی عددی | تشخیص رنگ بصری | تقسیم توجه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان ارشد کالیبراسیون | مهندسان سخت‌افزار رایانه | مهندسان برق | تکنسین‌ها و کارشناسان ارشد مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کارشناسان ارشد الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌استثنای رایانه | مهندسان تولید و ساخت | دانشمندان علوم مواد | تکنسین‌ها و کارشناسان ارشد مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان نانوسیستم‌ها | تکنسین‌ها و کارشناسان ارشد مهندسی نانوفناوری | مهندسان فوتونیک | تکنسین‌های فوتونیک | متخصصان تجهیزات شناسایی با امواج رادیویی (RFID) | مهندسان رباتیک | تکنسین‌های رباتیک | تکنسین‌های فرآوری نیمه‌هادی‌ها</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان سخت‌افزار رایانه | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان تولید و ساخت | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مهندسان فوتونیک | تکنسین‌های فوتونیک و اپتیک | متخصصان سامانه‌های شناسایی با امواج رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک | تکنسین‌های فرآوری و ساخت نیمه‌هادی‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نگارش | شنیدن فعال | ریاضیات | سخن گفتن | یادگیری فعال | علوم پایه | استراتژی‌های یادگیری | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | گوش دادن فعال | ریاضیات | سخن گفتن | یادگیری فعال | علوم | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | درک کتبی | درک شفاهی | استدلال ریاضی | بیان کتبی | سیالی ایده | ابتکار | حساسیت به مسئله | بیان شفاهی | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | وضوح گفتار | محاسبات عددی | انعطاف‌پذیری در نتیجه‌گیری | تشخیص گفتار | تجسم فضایی | سرعت ادراک</t>
+          <t>استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک کتبی | درک شفاهی | استدلال ریاضی | بیان کتبی | روانی ایده‌ها | اصالت | حساسیت به مسئله | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | وضوح گفتار | توانایی عددی | انعطاف‌پذیری بستار | تشخیص گفتار | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان ارشد فناوری هوافضا و عملیات پرواز | مهندسان خودرو | تکنسین‌ها و کارشناسان ارشد کالیبراسیون | مهندسان سخت‌افزار رایانه | مهندسان برق | تکنسین‌ها و کارشناسان ارشد مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کارشناسان ارشد الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌استثنای رایانه | دانشمندان علوم مواد | تکنسین‌ها و کارشناسان ارشد مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | مهندسان نانوسیستم‌ها | تکنسین‌ها و کارشناسان ارشد مهندسی نانوفناوری | تکنسین‌های فوتونیک | متخصصان تجهیزات شناسایی با امواج رادیویی (RFID) | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان سخت‌افزار رایانه | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک و اپتیک | متخصصان سامانه‌های شناسایی با امواج رادیویی | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نظارت | نگارش | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری | سخن گفتن | علوم پایه</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | سخن گفتن | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | رایانه و الکترونیک | مکانیک | ریاضیات | زبان انگلیسی | فیزیک | تولید و فرآوری | آموزش و تدریس</t>
+          <t>مهندسی و فناوری | طراحی | رایانه و الکترونیک | مکانیک | ریاضیات | زبان انگلیسی | فیزیک | تولید و فرآوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | سیالی ایده | ابتکار | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | تجسم فضایی | بیان شفاهی | بیان کتبی | دید نزدیک | انعطاف‌پذیری در نتیجه‌گیری | تشخیص گفتار | چابکی انگشتان | محاسبات عددی | سرعت ادراک | وضوح گفتار | تمایز رنگ‌ها | ثبات دست و بازو | توجه انتخابی | کنترل دقیق | چابکی دستی | تقسیم توجه | به خاطر سپاری</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | تجسم | بیان شفاهی | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری بستار | تشخیص گفتار | مهارت انگشتان | توانایی عددی | سرعت ادراکی | وضوح گفتار | تشخیص رنگ بصری | ثبات دست و بازو | توجه انتخابی | دقت کنترل | مهارت دستی | تقسیم توجه | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان ارشد فناوری هوافضا و عملیات پرواز | مهندسان هوافضا | مهندسان خودرو | مهندسان سخت‌افزار رایانه | اپراتورهای ماشین‌های ابزار CNC | برنامه‌نویسان ماشین‌های ابزار CNC | مهندسان برق | تکنسین‌ها و کارشناسان ارشد مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کارشناسان ارشد الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌استثنای رایانه | تکنسین‌ها و کارشناسان ارشد مهندسی صنایع | مهندسان تولید و ساخت | تکنسین‌ها و کارشناسان ارشد مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | تکنسین‌ها و کارشناسان ارشد مهندسی نانوفناوری | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | مهندسان خودرو | مهندسان سخت‌افزار رایانه | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | تفکر انتقادی | علوم پایه | شنیدن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | علوم | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | فیزیک | شیمی | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | آموزش و تدریس | طراحی | تولید و فرآوری | مکانیک | مدیریت و امور اداری</t>
+          <t>مهندسی و فناوری | فیزیک | شیمی | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | طراحی | تولید و فرآوری | مکانیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | حساسیت به مسئله | استدلال ریاضی | انعطاف‌پذیری در نتیجه‌گیری | ابتکار | وضوح گفتار | سیالی ایده | تشخیص گفتار | محاسبات عددی | توجه انتخابی | تجسم فضایی | دید دور</t>
+          <t>استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | استدلال ریاضی | انعطاف‌پذیری بستار | اصالت | وضوح گفتار | روانی ایده‌ها | تشخیص گفتار | توانایی عددی | توجه انتخابی | تجسم | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان بیوشیمی و بیوفیزیک | مهندسان زیستی و مهندسان پزشکی | مدیران توسعه محصول و فناوری سوخت‌های زیستی و بیودیزل | دانشمندان بیوانفورماتیک | مهندسان شیمی | تکنسین‌های شیمی | شیمیدانان | مهندسان پیل سوختی | تکنسین‌ها و کارشناسان ارشد مهندسی صنایع | مهندسان تولید و ساخت | مهندسان مواد | دانشمندان علوم مواد | تکنسین‌ها و کارشناسان ارشد مهندسی مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم‌ها | زیست‌شناسان مولکولی و سلولی | تکنسین‌ها و کارشناسان ارشد مهندسی نانوفناوری | مهندسان فوتونیک | تکنسین‌های فوتونیک | مهندسان رباتیک</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | مدیران توسعه محصول و فناوری زیست‌سوخت | متخصصان بیوانفورماتیک | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | مهندسان پیل سوختی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان تولید و ساخت | مهندسان متالورژی و مواد | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | زیست‌شناسان سلولی و مولکولی | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مهندسان فوتونیک | تکنسین‌های فوتونیک و اپتیک | مهندسان رباتیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | ریاضیات | شنیدن فعال | نگارش | سخن گفتن | علوم پایه | نظارت | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | ریاضیات | گوش دادن فعال | نگارش | سخن گفتن | علوم | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | طراحی | فیزیک | زبان انگلیسی | رایانه و الکترونیک | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ساختمان و سازه | مکانیک | ایمنی و امنیت عمومی | حقوق و مقررات دولتی</t>
+          <t>مهندسی و فناوری | ریاضیات | طراحی | فیزیک | زبان انگلیسی | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مکانیک | ایمنی و امنیت عمومی | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | درک کتبی | محاسبات عددی | حساسیت به مسئله | درک شفاهی | بیان کتبی | بیان شفاهی | وضوح گفتار | دید نزدیک | تشخیص گفتار | تجسم فضایی | مرتب‌سازی اطلاعات | ابتکار | سیالی ایده</t>
+          <t>استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | درک کتبی | توانایی عددی | حساسیت به مسئله | درک شفاهی | بیان کتبی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | تجسم | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان هوافضا | مهندسان خودرو | مدیران نیروگاه‌های زیست‌توده (بیومس) | مهندسان عمران | مهندسان برق | مهندسان انرژی، به‌استثنای باد و خورشید | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران تولید برق‌آبی | تکنسین‌ها و کارشناسان ارشد مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | مهندسان آب و فاضلاب | مدیران توسعه انرژی باد | مدیران بهره‌برداری مزارع بادی | تکنسین‌های تعمیر و نگهداری توربین بادی</t>
+          <t>مهندسان هوافضا | مهندسان خودرو | مدیران نیروگاه‌های زیست‌توده | مهندسان عمران | مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک | مهندسان آب و فاضلاب | مدیران توسعه پروژه‌های انرژی بادی | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | شنیدن فعال | ریاضیات | نظارت | یادگیری فعال | علوم پایه</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | ریاضیات | نظارت | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | ساختمان و سازه | ریاضیات | مکانیک | فیزیک | رایانه و الکترونیک | مدیریت و امور اداری | زبان انگلیسی</t>
+          <t>مهندسی و فناوری | طراحی | ساختمان و ساخت‌وساز | ریاضیات | مکانیک | فیزیک | رایانه و الکترونیک | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان کتبی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بیان شفاهی | سیالی ایده | استدلال استقرایی | درک شفاهی | مرتب‌سازی اطلاعات | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | ابتکار | دید نزدیک | وضوح گفتار | تشخیص گفتار | تجسم فضایی | انعطاف‌پذیری در نتیجه‌گیری | محاسبات عددی | دید دور | توجه انتخابی</t>
+          <t>بیان کتبی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بیان شفاهی | روانی ایده‌ها | استدلال استقرایی | درک شفاهی | ترتیب‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | اصالت | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | تجسم | انعطاف‌پذیری بستار | توانایی عددی | بینایی دور | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی و بیودیزل | مهندسان برق | تکنسین‌ها و کارشناسان ارشد مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌استثنای رایانه | ممیزان انرژی | مهندسان انرژی، به‌استثنای باد و خورشید | مهندسان پیل سوختی | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های انرژی زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران تولید برق‌آبی | مهندسان مکانیک | مدیران نصب سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | ارزیابان و نمایندگان فروش تجهیزات خورشیدی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | مهندسان آب و فاضلاب | مدیران توسعه انرژی باد | مهندسان انرژی باد | تکنسین‌های تعمیر و نگهداری توربین بادی</t>
+          <t>مدیران توسعه محصول و فناوری زیست‌سوخت | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | ممیزان انرژی | مهندسان انرژی، به‌جز بادی و خورشیدی | مهندسان پیل سوختی | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | مهندسان مکانیک | مدیران اجرای پروژه‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | مهندسان آب و فاضلاب | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی باد | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | ریاضیات | شنیدن فعال | نظارت | سخن گفتن | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | ریاضیات | گوش دادن فعال | نظارت | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>طراحی | ساختمان و سازه | مهندسی و فناوری | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>طراحی | ساختمان و ساخت‌وساز | مهندسی و فناوری | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | ابتکار | سیالی ایده | بیان شفاهی | انعطاف‌پذیری در نتیجه‌گیری | حساسیت به مسئله | توجه انتخابی | وضوح گفتار | تشخیص گفتار | محاسبات عددی</t>
+          <t>تجسم | بینایی نزدیک | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | اصالت | روانی ایده‌ها | بیان شفاهی | انعطاف‌پذیری بستار | حساسیت به مسئله | توجه انتخابی | وضوح گفتار | تشخیص گفتار | توانایی عددی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>معماران، به‌استثنای معماران منظر و طراحان شناورهای دریایی | مدیران معماری و مهندسی | تکنسین‌ها و کارشناسان ارشد کالیبراسیون | تکنسین‌ها و کارشناسان ارشد مهندسی عمران | مهندسان عمران | طراحان تجاری و صنعتی | برنامه‌نویسان ماشین‌های ابزار CNC | مدیران پروژه‌های ساختمانی | بازرسان ساختمان و سازه | مهندسان برق | تکنسین‌ها و کارشناسان ارشد مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به‌استثنای رایانه | مهندسان صنایع | خط‌کشان و لایه‌چینان فلز و پلاستیک | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان ارشد مهندسی مکانیک | مهندسان مکانیک | توسعه‌دهندگان نرم‌افزار | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | مدیران فنی و مهندسی و معماری | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | طراحان تجاری و صنعتی | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان صنایع | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | نقشه‌کشان مکانیک | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | توسعه‌دهندگان نرم‌افزار | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نظارت</t>
+          <t>گوش دادن فعال | نگارش | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | امور اداری | آموزش و تدریس | ایمنی و امنیت عمومی | جغرافیا</t>
+          <t>طراحی | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | اداری | آموزش و پرورش | ایمنی و امنیت عمومی | جغرافیا</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | دید نزدیک | تجسم فضایی | بیان شفاهی | بیان کتبی | تشخیص گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری در نتیجه‌گیری | استدلال ریاضی</t>
+          <t>درک کتبی | درک شفاهی | بینایی نزدیک | تجسم | بیان شفاهی | بیان کتبی | تشخیص گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | تکنسین‌ها و کارشناسان ارشد کالیبراسیون | تکنسین‌ها و کارشناسان ارشد مهندسی عمران | طراحان تجاری و صنعتی | مهندسان سخت‌افزار رایانه | برنامه‌نویسان ماشین‌های ابزار CNC | مهندسان برق | تکنسین‌ها و کارشناسان ارشد مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کارشناسان ارشد الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌استثنای رایانه | مهندسان صنایع | خط‌کشان و لایه‌چینان فلز و پلاستیک | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان ارشد مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های رباتیک</t>
+          <t>نقشه‌کشان معماری و عمران | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی عمران | طراحان تجاری و صنعتی | مهندسان سخت‌افزار رایانه | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان صنایع | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | نقشه‌کشان مکانیک | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | یادگیری فعال | ریاضیات | شنیدن فعال | درک مطلب | سخن گفتن | نگارش | نظارت</t>
+          <t>تفکر انتقادی | یادگیری فعال | ریاضیات | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | مکانیک | ریاضیات | زبان انگلیسی | فیزیک | رایانه و الکترونیک | تولید و فرآوری | آموزش و تدریس | خدمات مشتریان و خدمات فردی</t>
+          <t>طراحی | مهندسی و فناوری | مکانیک | ریاضیات | زبان انگلیسی | فیزیک | رایانه و الکترونیک | تولید و فرآوری | آموزش و پرورش | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | تجسم فضایی | استدلال ریاضی | توجه انتخابی | تشخیص گفتار | وضوح گفتار | درک شفاهی | بیان شفاهی | بیان کتبی | سیالی ایده | ابتکار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | درک کتبی | تمایز رنگ‌ها | چابکی انگشتان | انعطاف‌پذیری در نتیجه‌گیری | محاسبات عددی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | تجسم | استدلال ریاضی | توجه انتخابی | تشخیص گفتار | وضوح گفتار | درک شفاهی | بیان شفاهی | بیان کتبی | روانی ایده‌ها | اصالت | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | درک کتبی | تشخیص رنگ بصری | مهارت انگشتان | انعطاف‌پذیری بستار | توانایی عددی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | تکنسین‌ها و کارشناسان ارشد کالیبراسیون | تکنسین‌ها و کارشناسان ارشد مهندسی عمران | طراحان تجاری و صنعتی | برنامه‌نویسان ماشین‌های ابزار CNC | مهندسان برق | تکنسین‌ها و کارشناسان ارشد مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به‌استثنای رایانه | تکنسین‌ها و کارشناسان ارشد مهندسی صنایع | مهندسان صنایع | خط‌کشان و لایه‌چینان فلز و پلاستیک | ماشین‌کاران | تکنسین‌ها و کارشناسان ارشد مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مدل‌سازان الگو، فلز و پلاستیک | الگوپژوهان و الگوسازان فلز و پلاستیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>نقشه‌کشان معماری و عمران | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی عمران | طراحان تجاری و صنعتی | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مدل‌سازان فلز و پلاستیک | الگوسازان فلز و پلاستیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
